--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/pre LAM_HRM-2031-0172/Panel 02/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/pre LAM_HRM-2031-0172/Panel 02/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
@@ -419,22 +419,42 @@
     <row r="1">
       <c r="C1" t="inlineStr">
         <is>
-          <t>Distance 1</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Distance 2</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Angle</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>Outer Radius</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -446,20 +466,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fiducial 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>121.50454</v>
+        <v>17.28561</v>
       </c>
       <c r="D2" t="n">
-        <v>85.21742</v>
+        <v>16.88803</v>
       </c>
       <c r="E2" t="n">
-        <v>90.06434</v>
+        <v>17.07</v>
       </c>
       <c r="F2" t="n">
-        <v>519.07971</v>
+        <v>54.0799</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.35398</v>
+      </c>
+      <c r="H2" t="n">
+        <v>86.9722</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.81787</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +501,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>123.10052</v>
+        <v>17.24535</v>
       </c>
       <c r="D3" t="n">
-        <v>86.15663000000001</v>
+        <v>16.6057</v>
       </c>
       <c r="E3" t="n">
-        <v>91.54738999999999</v>
+        <v>17.13486</v>
       </c>
       <c r="F3" t="n">
-        <v>518.21188</v>
+        <v>56.51115</v>
+      </c>
+      <c r="G3" t="n">
+        <v>44.09099</v>
+      </c>
+      <c r="H3" t="n">
+        <v>85.07818</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.05177</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.81365</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +532,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>123.58806</v>
+        <v>17.03748</v>
       </c>
       <c r="D4" t="n">
-        <v>86.99876999999999</v>
+        <v>16.47753</v>
       </c>
       <c r="E4" t="n">
-        <v>93.56655000000001</v>
+        <v>16.99971</v>
       </c>
       <c r="F4" t="n">
-        <v>522.4981299999999</v>
+        <v>55.93923</v>
+      </c>
+      <c r="G4" t="n">
+        <v>43.34569</v>
+      </c>
+      <c r="H4" t="n">
+        <v>85.64661</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.05181</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.83733</v>
       </c>
     </row>
     <row r="5">
@@ -507,16 +563,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>124.31628</v>
+        <v>16.95405</v>
       </c>
       <c r="D5" t="n">
-        <v>87.76073</v>
+        <v>16.73705</v>
       </c>
       <c r="E5" t="n">
-        <v>92.54638</v>
+        <v>16.82479</v>
       </c>
       <c r="F5" t="n">
-        <v>519.25186</v>
+        <v>56.34738</v>
+      </c>
+      <c r="G5" t="n">
+        <v>42.54038</v>
+      </c>
+      <c r="H5" t="n">
+        <v>84.72613</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0508</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.85211</v>
       </c>
     </row>
     <row r="6">
@@ -526,16 +594,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>125.12398</v>
+        <v>16.75181</v>
       </c>
       <c r="D6" t="n">
-        <v>87.40653</v>
+        <v>16.60657</v>
       </c>
       <c r="E6" t="n">
-        <v>93.7816</v>
+        <v>16.62105</v>
       </c>
       <c r="F6" t="n">
-        <v>522.07354</v>
+        <v>55.90454</v>
+      </c>
+      <c r="G6" t="n">
+        <v>42.87921</v>
+      </c>
+      <c r="H6" t="n">
+        <v>86.50373999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.05122</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.85204</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +625,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>123.50435</v>
+        <v>17.26733</v>
       </c>
       <c r="D7" t="n">
-        <v>86.76488999999999</v>
+        <v>16.63898</v>
       </c>
       <c r="E7" t="n">
-        <v>93.03296</v>
+        <v>17.09657</v>
       </c>
       <c r="F7" t="n">
-        <v>518.4177100000001</v>
+        <v>56.54244</v>
+      </c>
+      <c r="G7" t="n">
+        <v>42.68713</v>
+      </c>
+      <c r="H7" t="n">
+        <v>85.4358</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.05211</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.78006</v>
       </c>
     </row>
     <row r="8">
@@ -564,16 +656,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>123.97154</v>
+        <v>16.98216</v>
       </c>
       <c r="D8" t="n">
-        <v>85.27934</v>
+        <v>16.371</v>
       </c>
       <c r="E8" t="n">
-        <v>92.86254</v>
+        <v>16.9382</v>
       </c>
       <c r="F8" t="n">
-        <v>513.63968</v>
+        <v>56.02783</v>
+      </c>
+      <c r="G8" t="n">
+        <v>43.71502</v>
+      </c>
+      <c r="H8" t="n">
+        <v>85.7346</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.05147</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.85353</v>
       </c>
     </row>
     <row r="9">
@@ -583,16 +687,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>125.26278</v>
+        <v>16.96392</v>
       </c>
       <c r="D9" t="n">
-        <v>86.45028000000001</v>
+        <v>16.51312</v>
       </c>
       <c r="E9" t="n">
-        <v>92.80367</v>
+        <v>16.7589</v>
       </c>
       <c r="F9" t="n">
-        <v>523.72346</v>
+        <v>55.62677</v>
+      </c>
+      <c r="G9" t="n">
+        <v>43.04859</v>
+      </c>
+      <c r="H9" t="n">
+        <v>84.5468</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.05083</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.82763</v>
       </c>
     </row>
     <row r="10">
@@ -602,27 +718,69 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>125.29724</v>
+        <v>16.97168</v>
       </c>
       <c r="D10" t="n">
-        <v>87.49478000000001</v>
+        <v>16.83801</v>
       </c>
       <c r="E10" t="n">
-        <v>91.24912999999999</v>
+        <v>16.85601</v>
       </c>
       <c r="F10" t="n">
-        <v>528.18571</v>
+        <v>56.21471</v>
+      </c>
+      <c r="G10" t="n">
+        <v>43.42363</v>
+      </c>
+      <c r="H10" t="n">
+        <v>86.88476</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.05145</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.77855</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Height</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Outer Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -634,14 +792,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Micro Bump 3</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.64039</v>
+        <v>16.97341</v>
       </c>
       <c r="D12" t="n">
-        <v>24.9873</v>
+        <v>16.79332</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.852</v>
+      </c>
+      <c r="F12" t="n">
+        <v>56.78508</v>
+      </c>
+      <c r="G12" t="n">
+        <v>42.73261</v>
+      </c>
+      <c r="H12" t="n">
+        <v>84.74558</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.05209</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.8546</v>
       </c>
     </row>
     <row r="13">
@@ -651,10 +827,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.691599999999999</v>
+        <v>17.1782</v>
       </c>
       <c r="D13" t="n">
-        <v>24.66834</v>
+        <v>16.63041</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.67082</v>
+      </c>
+      <c r="F13" t="n">
+        <v>56.17999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>43.47491</v>
+      </c>
+      <c r="H13" t="n">
+        <v>85.44504999999999</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.05048</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.84752</v>
       </c>
     </row>
     <row r="14">
@@ -664,10 +858,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.76003</v>
+        <v>16.99915</v>
       </c>
       <c r="D14" t="n">
-        <v>24.44868</v>
+        <v>16.68291</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.8201</v>
+      </c>
+      <c r="F14" t="n">
+        <v>57.26509</v>
+      </c>
+      <c r="G14" t="n">
+        <v>44.15348</v>
+      </c>
+      <c r="H14" t="n">
+        <v>86.58954</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.05064</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.82666</v>
       </c>
     </row>
     <row r="15">
@@ -677,10 +889,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.92625</v>
+        <v>16.94166</v>
       </c>
       <c r="D15" t="n">
-        <v>24.4039</v>
+        <v>16.89816</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.90645</v>
+      </c>
+      <c r="F15" t="n">
+        <v>56.7912</v>
+      </c>
+      <c r="G15" t="n">
+        <v>42.30499</v>
+      </c>
+      <c r="H15" t="n">
+        <v>85.22542</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.05158</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.85785</v>
       </c>
     </row>
     <row r="16">
@@ -690,10 +920,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.625859999999999</v>
+        <v>17.10725</v>
       </c>
       <c r="D16" t="n">
-        <v>24.0485</v>
+        <v>16.71079</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.91215</v>
+      </c>
+      <c r="F16" t="n">
+        <v>55.87431</v>
+      </c>
+      <c r="G16" t="n">
+        <v>43.21281</v>
+      </c>
+      <c r="H16" t="n">
+        <v>85.58540000000001</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.05051</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.85596</v>
       </c>
     </row>
     <row r="17">
@@ -703,10 +951,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.742470000000001</v>
+        <v>17.20235</v>
       </c>
       <c r="D17" t="n">
-        <v>24.40121</v>
+        <v>16.56</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.9865</v>
+      </c>
+      <c r="F17" t="n">
+        <v>55.64408</v>
+      </c>
+      <c r="G17" t="n">
+        <v>42.88069</v>
+      </c>
+      <c r="H17" t="n">
+        <v>83.9367</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.05164</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.84297</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +982,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.708410000000001</v>
+        <v>16.87412</v>
       </c>
       <c r="D18" t="n">
-        <v>24.68653</v>
+        <v>16.74854</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.84479</v>
+      </c>
+      <c r="F18" t="n">
+        <v>56.21717</v>
+      </c>
+      <c r="G18" t="n">
+        <v>42.32016</v>
+      </c>
+      <c r="H18" t="n">
+        <v>87.63064</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.05185</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.8637</v>
       </c>
     </row>
     <row r="19">
@@ -729,10 +1013,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.67869</v>
+        <v>16.98025</v>
       </c>
       <c r="D19" t="n">
-        <v>24.59756</v>
+        <v>16.80225</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.94787</v>
+      </c>
+      <c r="F19" t="n">
+        <v>55.43246</v>
+      </c>
+      <c r="G19" t="n">
+        <v>43.21715</v>
+      </c>
+      <c r="H19" t="n">
+        <v>86.33297</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.05046</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.85805</v>
       </c>
     </row>
     <row r="20">
@@ -742,10 +1044,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.47564</v>
+        <v>16.88142</v>
       </c>
       <c r="D20" t="n">
-        <v>24.94971</v>
+        <v>16.5856</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.78109</v>
+      </c>
+      <c r="F20" t="n">
+        <v>53.89348</v>
+      </c>
+      <c r="G20" t="n">
+        <v>43.0911</v>
+      </c>
+      <c r="H20" t="n">
+        <v>85.43255000000001</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.05088</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.83962</v>
       </c>
     </row>
     <row r="21">
@@ -766,17 +1086,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bump</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -788,26 +1103,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.99561</v>
+        <v>16.70687</v>
       </c>
       <c r="D22" t="n">
-        <v>16.81264</v>
+        <v>15.84042</v>
       </c>
       <c r="E22" t="n">
-        <v>16.85979</v>
+        <v>16.21158</v>
       </c>
       <c r="F22" t="n">
-        <v>42.58058</v>
+        <v>21.88277</v>
       </c>
       <c r="G22" t="n">
-        <v>0.05148</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.79838</v>
+        <v>34.67331</v>
       </c>
     </row>
     <row r="23">
@@ -817,22 +1129,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.63234</v>
+        <v>16.72452</v>
       </c>
       <c r="D23" t="n">
-        <v>16.96202</v>
+        <v>16.07165</v>
       </c>
       <c r="E23" t="n">
-        <v>16.64527</v>
+        <v>16.46085</v>
       </c>
       <c r="F23" t="n">
-        <v>42.86626</v>
+        <v>22.14286</v>
       </c>
       <c r="G23" t="n">
-        <v>0.05096</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.87753</v>
+        <v>34.5948</v>
       </c>
     </row>
     <row r="24">
@@ -842,22 +1151,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>17.11912</v>
+        <v>17.15387</v>
       </c>
       <c r="D24" t="n">
-        <v>17.12631</v>
+        <v>16.1872</v>
       </c>
       <c r="E24" t="n">
-        <v>17.01282</v>
+        <v>16.7827</v>
       </c>
       <c r="F24" t="n">
-        <v>43.11903</v>
+        <v>22.1983</v>
       </c>
       <c r="G24" t="n">
-        <v>0.05139</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.81099</v>
+        <v>34.75631</v>
       </c>
     </row>
     <row r="25">
@@ -867,22 +1173,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16.68208</v>
+        <v>16.79932</v>
       </c>
       <c r="D25" t="n">
-        <v>16.56754</v>
+        <v>16.47466</v>
       </c>
       <c r="E25" t="n">
-        <v>16.88656</v>
+        <v>16.65866</v>
       </c>
       <c r="F25" t="n">
-        <v>42.71591</v>
+        <v>22.40338</v>
       </c>
       <c r="G25" t="n">
-        <v>0.05005</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.86245</v>
+        <v>34.60017</v>
       </c>
     </row>
     <row r="26">
@@ -892,22 +1195,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.86639</v>
+        <v>16.98185</v>
       </c>
       <c r="D26" t="n">
-        <v>16.93061</v>
+        <v>16.12806</v>
       </c>
       <c r="E26" t="n">
-        <v>17.07107</v>
+        <v>16.74593</v>
       </c>
       <c r="F26" t="n">
-        <v>43.32032</v>
+        <v>21.85486</v>
       </c>
       <c r="G26" t="n">
-        <v>0.05053</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.82491</v>
+        <v>34.91865</v>
       </c>
     </row>
     <row r="27">
@@ -917,22 +1217,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17.2667</v>
+        <v>16.55422</v>
       </c>
       <c r="D27" t="n">
-        <v>16.49942</v>
+        <v>16.30253</v>
       </c>
       <c r="E27" t="n">
-        <v>16.91262</v>
+        <v>16.31561</v>
       </c>
       <c r="F27" t="n">
-        <v>42.76105</v>
+        <v>22.44291</v>
       </c>
       <c r="G27" t="n">
-        <v>0.05129</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.84323</v>
+        <v>34.3767</v>
       </c>
     </row>
     <row r="28">
@@ -942,22 +1239,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.84456</v>
+        <v>17.01401</v>
       </c>
       <c r="D28" t="n">
-        <v>16.85454</v>
+        <v>16.22516</v>
       </c>
       <c r="E28" t="n">
-        <v>17.03498</v>
+        <v>16.91513</v>
       </c>
       <c r="F28" t="n">
-        <v>42.73439</v>
+        <v>22.13103</v>
       </c>
       <c r="G28" t="n">
-        <v>0.05104</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.85616</v>
+        <v>34.26912</v>
       </c>
     </row>
     <row r="29">
@@ -967,22 +1261,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.99325</v>
+        <v>17.08836</v>
       </c>
       <c r="D29" t="n">
-        <v>16.76767</v>
+        <v>16.06096</v>
       </c>
       <c r="E29" t="n">
-        <v>17.1653</v>
+        <v>16.86643</v>
       </c>
       <c r="F29" t="n">
-        <v>44.26672</v>
+        <v>21.98464</v>
       </c>
       <c r="G29" t="n">
-        <v>0.05038</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.86167</v>
+        <v>34.74125</v>
       </c>
     </row>
     <row r="30">
@@ -992,22 +1283,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17.15102</v>
+        <v>17.01238</v>
       </c>
       <c r="D30" t="n">
-        <v>17.0092</v>
+        <v>16.09538</v>
       </c>
       <c r="E30" t="n">
-        <v>16.76898</v>
+        <v>17.00477</v>
       </c>
       <c r="F30" t="n">
-        <v>43.76128</v>
+        <v>21.86183</v>
       </c>
       <c r="G30" t="n">
-        <v>0.05063</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.84651</v>
+        <v>34.30047</v>
       </c>
     </row>
     <row r="31">
@@ -1064,28 +1352,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.76459</v>
+        <v>0.7415</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08244</v>
+        <v>0.08228000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>0.61881</v>
+        <v>0.61003</v>
       </c>
       <c r="F32" t="n">
-        <v>0.97575</v>
+        <v>0.97329</v>
       </c>
       <c r="G32" t="n">
-        <v>0.11055</v>
+        <v>0.11109</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00758</v>
+        <v>0.00766</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09496</v>
+        <v>0.09429</v>
       </c>
       <c r="J32" t="n">
-        <v>0.12832</v>
+        <v>0.12464</v>
       </c>
     </row>
     <row r="33">
@@ -1095,28 +1383,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.76064</v>
+        <v>0.76928</v>
       </c>
       <c r="D33" t="n">
-        <v>0.08263</v>
+        <v>0.08191</v>
       </c>
       <c r="E33" t="n">
-        <v>0.61693</v>
+        <v>0.6151</v>
       </c>
       <c r="F33" t="n">
-        <v>0.97514</v>
+        <v>0.97072</v>
       </c>
       <c r="G33" t="n">
-        <v>0.11088</v>
+        <v>0.10949</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00768</v>
+        <v>0.00772</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09353</v>
+        <v>0.09192</v>
       </c>
       <c r="J33" t="n">
-        <v>0.12882</v>
+        <v>0.12524</v>
       </c>
     </row>
     <row r="34">
@@ -1126,28 +1414,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.7595499999999999</v>
+        <v>0.76536</v>
       </c>
       <c r="D34" t="n">
-        <v>0.08153000000000001</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>0.61347</v>
+        <v>0.61238</v>
       </c>
       <c r="F34" t="n">
-        <v>0.97024</v>
+        <v>0.96821</v>
       </c>
       <c r="G34" t="n">
-        <v>0.10772</v>
+        <v>0.11265</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0077</v>
+        <v>0.00773</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09505</v>
+        <v>0.09607</v>
       </c>
       <c r="J34" t="n">
-        <v>0.12795</v>
+        <v>0.12888</v>
       </c>
     </row>
     <row r="35">
@@ -1157,28 +1445,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.74635</v>
+        <v>0.75972</v>
       </c>
       <c r="D35" t="n">
-        <v>0.08082</v>
+        <v>0.08223</v>
       </c>
       <c r="E35" t="n">
-        <v>0.61558</v>
+        <v>0.60366</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9639</v>
+        <v>0.9547</v>
       </c>
       <c r="G35" t="n">
-        <v>0.10983</v>
+        <v>0.1091</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00767</v>
+        <v>0.00768</v>
       </c>
       <c r="I35" t="n">
-        <v>0.09389</v>
+        <v>0.09357</v>
       </c>
       <c r="J35" t="n">
-        <v>0.12872</v>
+        <v>0.12513</v>
       </c>
     </row>
     <row r="36">
@@ -1188,28 +1476,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.7573299999999999</v>
+        <v>0.76567</v>
       </c>
       <c r="D36" t="n">
-        <v>0.08263</v>
+        <v>0.08128000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>0.61478</v>
+        <v>0.61941</v>
       </c>
       <c r="F36" t="n">
-        <v>0.98829</v>
+        <v>0.98288</v>
       </c>
       <c r="G36" t="n">
-        <v>0.11111</v>
+        <v>0.1114</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00771</v>
+        <v>0.00758</v>
       </c>
       <c r="I36" t="n">
-        <v>0.09245</v>
+        <v>0.09327000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>0.12933</v>
+        <v>0.13002</v>
       </c>
     </row>
     <row r="37">
@@ -1219,28 +1507,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.75873</v>
+        <v>0.74449</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08155999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="E37" t="n">
-        <v>0.62419</v>
+        <v>0.61087</v>
       </c>
       <c r="F37" t="n">
-        <v>0.98672</v>
+        <v>0.9744699999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>0.11109</v>
+        <v>0.11059</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00779</v>
+        <v>0.00761</v>
       </c>
       <c r="I37" t="n">
-        <v>0.09333</v>
+        <v>0.09455</v>
       </c>
       <c r="J37" t="n">
-        <v>0.12858</v>
+        <v>0.12905</v>
       </c>
     </row>
     <row r="38">
@@ -1250,28 +1538,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.7573800000000001</v>
+        <v>0.7529400000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08173</v>
+        <v>0.08166</v>
       </c>
       <c r="E38" t="n">
-        <v>0.60909</v>
+        <v>0.61872</v>
       </c>
       <c r="F38" t="n">
-        <v>0.98137</v>
+        <v>0.97251</v>
       </c>
       <c r="G38" t="n">
-        <v>0.11007</v>
+        <v>0.11042</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00768</v>
+        <v>0.0078</v>
       </c>
       <c r="I38" t="n">
-        <v>0.09155000000000001</v>
+        <v>0.09697</v>
       </c>
       <c r="J38" t="n">
-        <v>0.12833</v>
+        <v>0.12595</v>
       </c>
     </row>
     <row r="39">
@@ -1281,28 +1569,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.76725</v>
+        <v>0.76535</v>
       </c>
       <c r="D39" t="n">
-        <v>0.08222</v>
+        <v>0.08266</v>
       </c>
       <c r="E39" t="n">
-        <v>0.60509</v>
+        <v>0.62229</v>
       </c>
       <c r="F39" t="n">
-        <v>0.96854</v>
+        <v>0.96549</v>
       </c>
       <c r="G39" t="n">
-        <v>0.11313</v>
+        <v>0.11253</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00769</v>
+        <v>0.00759</v>
       </c>
       <c r="I39" t="n">
-        <v>0.09651999999999999</v>
+        <v>0.09438000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>0.12987</v>
+        <v>0.12915</v>
       </c>
     </row>
     <row r="40">
@@ -1312,28 +1600,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.77739</v>
+        <v>0.76259</v>
       </c>
       <c r="D40" t="n">
-        <v>0.08194</v>
+        <v>0.08251</v>
       </c>
       <c r="E40" t="n">
-        <v>0.61319</v>
+        <v>0.61626</v>
       </c>
       <c r="F40" t="n">
-        <v>0.97056</v>
+        <v>0.97244</v>
       </c>
       <c r="G40" t="n">
-        <v>0.11078</v>
+        <v>0.10919</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00763</v>
+        <v>0.00774</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0948</v>
+        <v>0.09444</v>
       </c>
       <c r="J40" t="n">
-        <v>0.12621</v>
+        <v>0.12849</v>
       </c>
     </row>
   </sheetData>
